--- a/2 FINANCE/TRESORERIE/2026 1028 Modèle Pop Tables - Trésorerie et mois de survie sur 36 mois.xlsx
+++ b/2 FINANCE/TRESORERIE/2026 1028 Modèle Pop Tables - Trésorerie et mois de survie sur 36 mois.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vians\Documents\Claude\Projects\HEC-GEMM-Groupe-7\2 FINANCE\TRESORERIE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D8E01C-6AF4-4710-ADDB-6D5E9A87B7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A440C5-4377-4CF4-9871-ACC2F192D277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{2D54D8BB-BD50-4D46-AD8E-735E0D6561AC}"/>
   </bookViews>
@@ -338,7 +338,7 @@
     <t>Suivi mensuel de la trésorerie (36 mois)</t>
   </si>
   <si>
-    <t>SIMULATION mise à jour le 28/10/2026 (soir), avant levée de fonds : flux repris du modèle Pop Tables (onglet « Budget 36 mois », revu par le responsable Finance, H), selon les décisions D-02 à D-20. Ventes encaissées TTC : places à l'unité en pré-vente le mois qui précède la soirée (D-04), privatisations le mois de la soirée (H). TVA payée aux fournisseurs et reversée à l'État dans « Impôts et TVA ». Investissements (site D-19, matériel) et frais d'ouverture des villes dans « Autres décaissements ». Impôt sur les sociétés non compté. Seul financement compté : l'apport de 7 000 € (H). À remplacer par les montants constatés.</t>
+    <t>SIMULATION mise à jour le 29/10/2026, avant levée de fonds : flux repris du modèle Pop Tables (onglet « Budget 36 mois », référence décidée D-21), selon les décisions D-02 à D-26. Ventes encaissées TTC : places à l'unité en pré-vente le mois qui précède la soirée (D-04), privatisations le mois de la soirée (H). TVA payée aux fournisseurs et reversée à l'État dans « Impôts et TVA ». Investissements (site D-19, matériel) et frais d'ouverture des villes dans « Autres décaissements ». Impôt sur les sociétés non compté. Seul financement compté : la love money de 70 000 € en novembre 2026 (D-26), ligne « Apports ». À remplacer par les montants constatés.</t>
   </si>
   <si>
     <t>H : moyenne des mois à consommation positive de la simulation sur 36 mois (ligne 9), à remplacer par la consommation constatée</t>
@@ -350,7 +350,7 @@
     <t>Pop Tables : soirées gastronomiques éphémères sur le segment du luxe ; places à l'unité en pré-vente et privatisations de salle. Sources : 1 DIRECTION/STRATEGIE/2026 1028 Pop Tables - Cadre de référence (D-02 à D-19) et Business Model Canvas V5 (D-20).</t>
   </si>
   <si>
-    <t>Mis à jour le 28/10/2026 (soir) : simulation sur 36 mois reprise du budget Pop Tables revu par le responsable Finance ; la société n'est pas créée, aucun relevé n'existe. Tous les montants sont des hypothèses (H).</t>
+    <t>Mis à jour le 29/10/2026 : simulation sur 36 mois reprise du budget Pop Tables (D-21), villes selon D-25, love money de 70 000 € (D-26) ; la société n'est pas créée, aucun relevé n'existe. Tous les montants sont des hypothèses (H).</t>
   </si>
 </sst>
 </file>
@@ -1630,143 +1630,143 @@
       </c>
       <c r="D7" s="18">
         <f t="shared" ref="D7:N7" si="1">IF(C30&lt;&gt;"",C30,C29)</f>
-        <v>-17763</v>
+        <v>45237</v>
       </c>
       <c r="E7" s="18">
         <f t="shared" si="1"/>
-        <v>-11514</v>
+        <v>51486</v>
       </c>
       <c r="F7" s="18">
         <f t="shared" si="1"/>
-        <v>-3016.6299999999974</v>
+        <v>59983.37</v>
       </c>
       <c r="G7" s="18">
         <f t="shared" si="1"/>
-        <v>-13995.629999999997</v>
+        <v>49004.37</v>
       </c>
       <c r="H7" s="18">
         <f t="shared" si="1"/>
-        <v>-52928.88</v>
+        <v>10071.120000000003</v>
       </c>
       <c r="I7" s="18">
         <f t="shared" si="1"/>
-        <v>-38639.17</v>
+        <v>24360.83</v>
       </c>
       <c r="J7" s="18">
         <f t="shared" si="1"/>
-        <v>-36919.81</v>
+        <v>26080.190000000002</v>
       </c>
       <c r="K7" s="18">
         <f t="shared" si="1"/>
-        <v>-34340.699999999997</v>
+        <v>28659.300000000003</v>
       </c>
       <c r="L7" s="18">
         <f t="shared" si="1"/>
-        <v>-44263.33</v>
+        <v>18736.670000000002</v>
       </c>
       <c r="M7" s="18">
         <f t="shared" si="1"/>
-        <v>-35674.33</v>
+        <v>27325.670000000002</v>
       </c>
       <c r="N7" s="18">
         <f t="shared" si="1"/>
-        <v>-40242.630000000005</v>
+        <v>22757.37</v>
       </c>
       <c r="O7" s="18">
         <f t="shared" ref="O7" si="2">IF(N30&lt;&gt;"",N30,N29)</f>
-        <v>-8551.1700000000055</v>
+        <v>54448.83</v>
       </c>
       <c r="P7" s="18">
         <f t="shared" ref="P7" si="3">IF(O30&lt;&gt;"",O30,O29)</f>
-        <v>27445.630000000012</v>
+        <v>90885.630000000019</v>
       </c>
       <c r="Q7" s="18">
         <f t="shared" ref="Q7" si="4">IF(P30&lt;&gt;"",P30,P29)</f>
-        <v>69142.430000000022</v>
+        <v>133022.43000000005</v>
       </c>
       <c r="R7" s="18">
         <f t="shared" ref="R7" si="5">IF(Q30&lt;&gt;"",Q30,Q29)</f>
-        <v>109803.03000000006</v>
+        <v>174043.03000000009</v>
       </c>
       <c r="S7" s="18">
         <f t="shared" ref="S7" si="6">IF(R30&lt;&gt;"",R30,R29)</f>
-        <v>146472.32000000009</v>
+        <v>211112.32000000012</v>
       </c>
       <c r="T7" s="18">
         <f t="shared" ref="T7" si="7">IF(S30&lt;&gt;"",S30,S29)</f>
-        <v>183141.61000000013</v>
+        <v>248181.61000000016</v>
       </c>
       <c r="U7" s="18">
         <f t="shared" ref="U7" si="8">IF(T30&lt;&gt;"",T30,T29)</f>
-        <v>219810.90000000017</v>
+        <v>285250.9000000002</v>
       </c>
       <c r="V7" s="18">
         <f t="shared" ref="V7" si="9">IF(U30&lt;&gt;"",U30,U29)</f>
-        <v>256480.19000000021</v>
+        <v>322320.19000000024</v>
       </c>
       <c r="W7" s="18">
         <f t="shared" ref="W7" si="10">IF(V30&lt;&gt;"",V30,V29)</f>
-        <v>293149.48000000021</v>
+        <v>359389.48000000027</v>
       </c>
       <c r="X7" s="18">
         <f t="shared" ref="X7" si="11">IF(W30&lt;&gt;"",W30,W29)</f>
-        <v>282818.77000000025</v>
+        <v>349458.77000000031</v>
       </c>
       <c r="Y7" s="18">
         <f t="shared" ref="Y7" si="12">IF(X30&lt;&gt;"",X30,X29)</f>
-        <v>342103.96000000025</v>
+        <v>408703.96000000031</v>
       </c>
       <c r="Z7" s="18">
         <f t="shared" ref="Z7" si="13">IF(Y30&lt;&gt;"",Y30,Y29)</f>
-        <v>364684.14000000025</v>
+        <v>431724.14000000036</v>
       </c>
       <c r="AA7" s="18">
         <f t="shared" ref="AA7" si="14">IF(Z30&lt;&gt;"",Z30,Z29)</f>
-        <v>433353.43000000028</v>
+        <v>500793.4300000004</v>
       </c>
       <c r="AB7" s="18">
         <f t="shared" ref="AB7" si="15">IF(AA30&lt;&gt;"",AA30,AA29)</f>
-        <v>460328.87000000029</v>
+        <v>527728.87000000034</v>
       </c>
       <c r="AC7" s="18">
         <f t="shared" ref="AC7" si="16">IF(AB30&lt;&gt;"",AB30,AB29)</f>
-        <v>494454.1300000003</v>
+        <v>561854.13000000035</v>
       </c>
       <c r="AD7" s="18">
         <f t="shared" ref="AD7" si="17">IF(AC30&lt;&gt;"",AC30,AC29)</f>
-        <v>527179.39000000036</v>
+        <v>594579.39000000036</v>
       </c>
       <c r="AE7" s="18">
         <f t="shared" ref="AE7" si="18">IF(AD30&lt;&gt;"",AD30,AD29)</f>
-        <v>559904.65000000037</v>
+        <v>627304.65000000037</v>
       </c>
       <c r="AF7" s="18">
         <f t="shared" ref="AF7" si="19">IF(AE30&lt;&gt;"",AE30,AE29)</f>
-        <v>592629.91000000038</v>
+        <v>660029.91000000038</v>
       </c>
       <c r="AG7" s="18">
         <f t="shared" ref="AG7" si="20">IF(AF30&lt;&gt;"",AF30,AF29)</f>
-        <v>625355.17000000039</v>
+        <v>692755.17000000039</v>
       </c>
       <c r="AH7" s="18">
         <f t="shared" ref="AH7" si="21">IF(AG30&lt;&gt;"",AG30,AG29)</f>
-        <v>658080.4300000004</v>
+        <v>725480.4300000004</v>
       </c>
       <c r="AI7" s="18">
         <f t="shared" ref="AI7" si="22">IF(AH30&lt;&gt;"",AH30,AH29)</f>
-        <v>690805.69000000041</v>
+        <v>758205.69000000041</v>
       </c>
       <c r="AJ7" s="18">
         <f t="shared" ref="AJ7" si="23">IF(AI30&lt;&gt;"",AI30,AI29)</f>
-        <v>629530.95000000042</v>
+        <v>696930.95000000042</v>
       </c>
       <c r="AK7" s="18">
         <f t="shared" ref="AK7" si="24">IF(AJ30&lt;&gt;"",AJ30,AJ29)</f>
-        <v>741258.00000000047</v>
+        <v>808658.00000000047</v>
       </c>
       <c r="AL7" s="18">
         <f t="shared" ref="AL7" si="25">IF(AK30&lt;&gt;"",AK30,AK29)</f>
-        <v>775735.05000000051</v>
+        <v>843135.05000000051</v>
       </c>
     </row>
     <row r="8" spans="1:38" ht="13" x14ac:dyDescent="0.3">
@@ -2051,10 +2051,10 @@
       </c>
       <c r="B11" s="18">
         <f>SUM(C11:AL11)</f>
-        <v>7000</v>
+        <v>70000</v>
       </c>
       <c r="C11" s="17">
-        <v>7000</v>
+        <v>70000</v>
       </c>
       <c r="D11" s="17">
         <v>0</v>
@@ -2519,11 +2519,11 @@
       </c>
       <c r="B15" s="19">
         <f>SUM(C15:AL15)</f>
-        <v>7298000</v>
+        <v>7361000</v>
       </c>
       <c r="C15" s="19">
         <f t="shared" ref="C15:N15" si="26">SUM(C9:C14)</f>
-        <v>7000</v>
+        <v>70000</v>
       </c>
       <c r="D15" s="19">
         <f t="shared" si="26"/>
@@ -3572,13 +3572,13 @@
         <v>4696.93</v>
       </c>
       <c r="O24" s="17">
-        <v>16779.63</v>
+        <v>16739.63</v>
       </c>
       <c r="P24" s="17">
-        <v>15779.63</v>
+        <v>15739.63</v>
       </c>
       <c r="Q24" s="17">
-        <v>17115.830000000002</v>
+        <v>17155.830000000002</v>
       </c>
       <c r="R24" s="17">
         <v>21107.14</v>
@@ -3599,16 +3599,16 @@
         <v>21107.14</v>
       </c>
       <c r="X24" s="17">
-        <v>18482.32</v>
+        <v>18522.32</v>
       </c>
       <c r="Y24" s="17">
-        <v>20196.25</v>
+        <v>20156.25</v>
       </c>
       <c r="Z24" s="17">
         <v>21107.14</v>
       </c>
       <c r="AA24" s="17">
-        <v>37964.11</v>
+        <v>38004.11</v>
       </c>
       <c r="AB24" s="17">
         <v>40214.29</v>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="B25" s="18">
         <f>SUM(C25:AL25)</f>
-        <v>757205.21</v>
+        <v>752805.21</v>
       </c>
       <c r="C25" s="17">
         <v>18702</v>
@@ -3689,40 +3689,40 @@
         <v>14140.54</v>
       </c>
       <c r="O25" s="17">
-        <v>22586.55</v>
+        <v>22186.55</v>
       </c>
       <c r="P25" s="17">
-        <v>17586.55</v>
+        <v>17186.55</v>
       </c>
       <c r="Q25" s="17">
-        <v>17586.55</v>
+        <v>17186.55</v>
       </c>
       <c r="R25" s="17">
-        <v>17586.55</v>
+        <v>17186.55</v>
       </c>
       <c r="S25" s="17">
-        <v>17586.55</v>
+        <v>17186.55</v>
       </c>
       <c r="T25" s="17">
-        <v>17586.55</v>
+        <v>17186.55</v>
       </c>
       <c r="U25" s="17">
-        <v>17586.55</v>
+        <v>17186.55</v>
       </c>
       <c r="V25" s="17">
-        <v>17586.55</v>
+        <v>17186.55</v>
       </c>
       <c r="W25" s="17">
-        <v>17586.55</v>
+        <v>17186.55</v>
       </c>
       <c r="X25" s="17">
         <v>27579.759999999998</v>
       </c>
       <c r="Y25" s="17">
-        <v>32586.55</v>
+        <v>32186.55</v>
       </c>
       <c r="Z25" s="17">
-        <v>32586.55</v>
+        <v>32186.55</v>
       </c>
       <c r="AA25" s="17">
         <v>45489.760000000002</v>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="B26" s="19">
         <f>SUM(C26:AL26)</f>
-        <v>6489539.6900000023</v>
+        <v>6485139.6900000023</v>
       </c>
       <c r="C26" s="19">
         <f t="shared" ref="C26:N26" si="28">SUM(C17:C25)</f>
@@ -3819,55 +3819,55 @@
       </c>
       <c r="O26" s="19">
         <f t="shared" ref="O26:AL26" si="29">SUM(O17:O25)</f>
-        <v>161003.19999999998</v>
+        <v>160563.19999999998</v>
       </c>
       <c r="P26" s="19">
         <f t="shared" si="29"/>
-        <v>155303.19999999998</v>
+        <v>154863.19999999998</v>
       </c>
       <c r="Q26" s="19">
         <f t="shared" si="29"/>
-        <v>156339.39999999997</v>
+        <v>155979.39999999997</v>
       </c>
       <c r="R26" s="19">
         <f t="shared" si="29"/>
-        <v>160330.70999999996</v>
+        <v>159930.70999999996</v>
       </c>
       <c r="S26" s="19">
         <f t="shared" si="29"/>
-        <v>160330.70999999996</v>
+        <v>159930.70999999996</v>
       </c>
       <c r="T26" s="19">
         <f t="shared" si="29"/>
-        <v>160330.70999999996</v>
+        <v>159930.70999999996</v>
       </c>
       <c r="U26" s="19">
         <f t="shared" si="29"/>
-        <v>160330.70999999996</v>
+        <v>159930.70999999996</v>
       </c>
       <c r="V26" s="19">
         <f t="shared" si="29"/>
-        <v>160330.70999999996</v>
+        <v>159930.70999999996</v>
       </c>
       <c r="W26" s="19">
         <f t="shared" si="29"/>
-        <v>160330.70999999996</v>
+        <v>159930.70999999996</v>
       </c>
       <c r="X26" s="19">
         <f t="shared" si="29"/>
-        <v>137714.81</v>
+        <v>137754.81</v>
       </c>
       <c r="Y26" s="19">
         <f t="shared" si="29"/>
-        <v>174419.81999999998</v>
+        <v>173979.81999999998</v>
       </c>
       <c r="Z26" s="19">
         <f t="shared" si="29"/>
-        <v>175330.70999999996</v>
+        <v>174930.70999999996</v>
       </c>
       <c r="AA26" s="19">
         <f t="shared" si="29"/>
-        <v>367024.56</v>
+        <v>367064.56</v>
       </c>
       <c r="AB26" s="19">
         <f t="shared" si="29"/>
@@ -3962,11 +3962,11 @@
       </c>
       <c r="B28" s="19">
         <f>SUM(C28:AL28)</f>
-        <v>808460.31000000052</v>
+        <v>875860.31000000052</v>
       </c>
       <c r="C28" s="19">
         <f t="shared" ref="C28:N28" si="30">C15-C26</f>
-        <v>-17763</v>
+        <v>45237</v>
       </c>
       <c r="D28" s="19">
         <f t="shared" si="30"/>
@@ -4014,55 +4014,55 @@
       </c>
       <c r="O28" s="19">
         <f t="shared" ref="O28:AL28" si="31">O15-O26</f>
-        <v>35996.800000000017</v>
+        <v>36436.800000000017</v>
       </c>
       <c r="P28" s="19">
         <f t="shared" si="31"/>
-        <v>41696.800000000017</v>
+        <v>42136.800000000017</v>
       </c>
       <c r="Q28" s="19">
         <f t="shared" si="31"/>
-        <v>40660.600000000035</v>
+        <v>41020.600000000035</v>
       </c>
       <c r="R28" s="19">
         <f t="shared" si="31"/>
-        <v>36669.290000000037</v>
+        <v>37069.290000000037</v>
       </c>
       <c r="S28" s="19">
         <f t="shared" si="31"/>
-        <v>36669.290000000037</v>
+        <v>37069.290000000037</v>
       </c>
       <c r="T28" s="19">
         <f t="shared" si="31"/>
-        <v>36669.290000000037</v>
+        <v>37069.290000000037</v>
       </c>
       <c r="U28" s="19">
         <f t="shared" si="31"/>
-        <v>36669.290000000037</v>
+        <v>37069.290000000037</v>
       </c>
       <c r="V28" s="19">
         <f t="shared" si="31"/>
-        <v>36669.290000000037</v>
+        <v>37069.290000000037</v>
       </c>
       <c r="W28" s="19">
         <f t="shared" si="31"/>
-        <v>-10330.709999999963</v>
+        <v>-9930.7099999999627</v>
       </c>
       <c r="X28" s="19">
         <f t="shared" si="31"/>
-        <v>59285.19</v>
+        <v>59245.19</v>
       </c>
       <c r="Y28" s="19">
         <f t="shared" si="31"/>
-        <v>22580.180000000022</v>
+        <v>23020.180000000022</v>
       </c>
       <c r="Z28" s="19">
         <f t="shared" si="31"/>
-        <v>68669.290000000037</v>
+        <v>69069.290000000037</v>
       </c>
       <c r="AA28" s="19">
         <f t="shared" si="31"/>
-        <v>26975.440000000002</v>
+        <v>26935.440000000002</v>
       </c>
       <c r="AB28" s="19">
         <f t="shared" si="31"/>
@@ -4115,151 +4115,151 @@
       </c>
       <c r="B29" s="19">
         <f>AL29</f>
-        <v>808460.31000000052</v>
+        <v>875860.31000000052</v>
       </c>
       <c r="C29" s="19">
         <f t="shared" ref="C29:N29" si="32">C7+C28</f>
-        <v>-17763</v>
+        <v>45237</v>
       </c>
       <c r="D29" s="19">
         <f t="shared" si="32"/>
-        <v>-11514</v>
+        <v>51486</v>
       </c>
       <c r="E29" s="19">
         <f t="shared" si="32"/>
-        <v>-3016.6299999999974</v>
+        <v>59983.37</v>
       </c>
       <c r="F29" s="19">
         <f t="shared" si="32"/>
-        <v>-13995.629999999997</v>
+        <v>49004.37</v>
       </c>
       <c r="G29" s="19">
         <f t="shared" si="32"/>
-        <v>-52928.88</v>
+        <v>10071.120000000003</v>
       </c>
       <c r="H29" s="19">
         <f t="shared" si="32"/>
-        <v>-38639.17</v>
+        <v>24360.83</v>
       </c>
       <c r="I29" s="19">
         <f t="shared" si="32"/>
-        <v>-36919.81</v>
+        <v>26080.190000000002</v>
       </c>
       <c r="J29" s="19">
         <f t="shared" si="32"/>
-        <v>-34340.699999999997</v>
+        <v>28659.300000000003</v>
       </c>
       <c r="K29" s="19">
         <f t="shared" si="32"/>
-        <v>-44263.33</v>
+        <v>18736.670000000002</v>
       </c>
       <c r="L29" s="19">
         <f t="shared" si="32"/>
-        <v>-35674.33</v>
+        <v>27325.670000000002</v>
       </c>
       <c r="M29" s="19">
         <f t="shared" si="32"/>
-        <v>-40242.630000000005</v>
+        <v>22757.37</v>
       </c>
       <c r="N29" s="19">
         <f t="shared" si="32"/>
-        <v>-8551.1700000000055</v>
+        <v>54448.83</v>
       </c>
       <c r="O29" s="19">
         <f t="shared" ref="O29:AL29" si="33">O7+O28</f>
-        <v>27445.630000000012</v>
+        <v>90885.630000000019</v>
       </c>
       <c r="P29" s="19">
         <f t="shared" si="33"/>
-        <v>69142.430000000022</v>
+        <v>133022.43000000005</v>
       </c>
       <c r="Q29" s="19">
         <f t="shared" si="33"/>
-        <v>109803.03000000006</v>
+        <v>174043.03000000009</v>
       </c>
       <c r="R29" s="19">
         <f t="shared" si="33"/>
-        <v>146472.32000000009</v>
+        <v>211112.32000000012</v>
       </c>
       <c r="S29" s="19">
         <f t="shared" si="33"/>
-        <v>183141.61000000013</v>
+        <v>248181.61000000016</v>
       </c>
       <c r="T29" s="19">
         <f t="shared" si="33"/>
-        <v>219810.90000000017</v>
+        <v>285250.9000000002</v>
       </c>
       <c r="U29" s="19">
         <f t="shared" si="33"/>
-        <v>256480.19000000021</v>
+        <v>322320.19000000024</v>
       </c>
       <c r="V29" s="19">
         <f t="shared" si="33"/>
-        <v>293149.48000000021</v>
+        <v>359389.48000000027</v>
       </c>
       <c r="W29" s="19">
         <f t="shared" si="33"/>
-        <v>282818.77000000025</v>
+        <v>349458.77000000031</v>
       </c>
       <c r="X29" s="19">
         <f t="shared" si="33"/>
-        <v>342103.96000000025</v>
+        <v>408703.96000000031</v>
       </c>
       <c r="Y29" s="19">
         <f t="shared" si="33"/>
-        <v>364684.14000000025</v>
+        <v>431724.14000000036</v>
       </c>
       <c r="Z29" s="19">
         <f t="shared" si="33"/>
-        <v>433353.43000000028</v>
+        <v>500793.4300000004</v>
       </c>
       <c r="AA29" s="19">
         <f t="shared" si="33"/>
-        <v>460328.87000000029</v>
+        <v>527728.87000000034</v>
       </c>
       <c r="AB29" s="19">
         <f t="shared" si="33"/>
-        <v>494454.1300000003</v>
+        <v>561854.13000000035</v>
       </c>
       <c r="AC29" s="19">
         <f t="shared" si="33"/>
-        <v>527179.39000000036</v>
+        <v>594579.39000000036</v>
       </c>
       <c r="AD29" s="19">
         <f t="shared" si="33"/>
-        <v>559904.65000000037</v>
+        <v>627304.65000000037</v>
       </c>
       <c r="AE29" s="19">
         <f t="shared" si="33"/>
-        <v>592629.91000000038</v>
+        <v>660029.91000000038</v>
       </c>
       <c r="AF29" s="19">
         <f t="shared" si="33"/>
-        <v>625355.17000000039</v>
+        <v>692755.17000000039</v>
       </c>
       <c r="AG29" s="19">
         <f t="shared" si="33"/>
-        <v>658080.4300000004</v>
+        <v>725480.4300000004</v>
       </c>
       <c r="AH29" s="19">
         <f t="shared" si="33"/>
-        <v>690805.69000000041</v>
+        <v>758205.69000000041</v>
       </c>
       <c r="AI29" s="19">
         <f t="shared" si="33"/>
-        <v>629530.95000000042</v>
+        <v>696930.95000000042</v>
       </c>
       <c r="AJ29" s="19">
         <f t="shared" si="33"/>
-        <v>741258.00000000047</v>
+        <v>808658.00000000047</v>
       </c>
       <c r="AK29" s="19">
         <f t="shared" si="33"/>
-        <v>775735.05000000051</v>
+        <v>843135.05000000051</v>
       </c>
       <c r="AL29" s="19">
         <f t="shared" si="33"/>
-        <v>808460.31000000052</v>
+        <v>875860.31000000052</v>
       </c>
     </row>
     <row r="30" spans="1:38" x14ac:dyDescent="0.25">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="B34" s="19">
         <f>SUM(C34:AL34)</f>
-        <v>-801460.31000000052</v>
+        <v>-805860.31000000052</v>
       </c>
       <c r="C34" s="19">
         <f t="shared" ref="C34:N34" si="36">C26-C9-C10-C14</f>
@@ -4594,55 +4594,55 @@
       </c>
       <c r="O34" s="19">
         <f t="shared" ref="O34:AL34" si="37">O26-O9-O10-O14</f>
-        <v>-35996.800000000017</v>
+        <v>-36436.800000000017</v>
       </c>
       <c r="P34" s="19">
         <f t="shared" si="37"/>
-        <v>-41696.800000000017</v>
+        <v>-42136.800000000017</v>
       </c>
       <c r="Q34" s="19">
         <f t="shared" si="37"/>
-        <v>-40660.600000000035</v>
+        <v>-41020.600000000035</v>
       </c>
       <c r="R34" s="19">
         <f t="shared" si="37"/>
-        <v>-36669.290000000037</v>
+        <v>-37069.290000000037</v>
       </c>
       <c r="S34" s="19">
         <f t="shared" si="37"/>
-        <v>-36669.290000000037</v>
+        <v>-37069.290000000037</v>
       </c>
       <c r="T34" s="19">
         <f t="shared" si="37"/>
-        <v>-36669.290000000037</v>
+        <v>-37069.290000000037</v>
       </c>
       <c r="U34" s="19">
         <f t="shared" si="37"/>
-        <v>-36669.290000000037</v>
+        <v>-37069.290000000037</v>
       </c>
       <c r="V34" s="19">
         <f t="shared" si="37"/>
-        <v>-36669.290000000037</v>
+        <v>-37069.290000000037</v>
       </c>
       <c r="W34" s="19">
         <f t="shared" si="37"/>
-        <v>10330.709999999963</v>
+        <v>9930.7099999999627</v>
       </c>
       <c r="X34" s="19">
         <f t="shared" si="37"/>
-        <v>-59285.19</v>
+        <v>-59245.19</v>
       </c>
       <c r="Y34" s="19">
         <f t="shared" si="37"/>
-        <v>-22580.180000000022</v>
+        <v>-23020.180000000022</v>
       </c>
       <c r="Z34" s="19">
         <f t="shared" si="37"/>
-        <v>-68669.290000000037</v>
+        <v>-69069.290000000037</v>
       </c>
       <c r="AA34" s="19">
         <f t="shared" si="37"/>
-        <v>-26975.440000000002</v>
+        <v>-26935.440000000002</v>
       </c>
       <c r="AB34" s="19">
         <f t="shared" si="37"/>
@@ -4696,7 +4696,7 @@
       <c r="B35" s="2"/>
       <c r="C35" s="21">
         <f t="shared" ref="C35:N35" si="38">IF(C34&gt;0,IF(C30&lt;&gt;"",C30,C29)/C34,0)</f>
-        <v>-0.71732019545289338</v>
+        <v>1.8267980454710657</v>
       </c>
       <c r="D35" s="21">
         <f t="shared" si="38"/>
@@ -4708,11 +4708,11 @@
       </c>
       <c r="F35" s="21">
         <f t="shared" si="38"/>
-        <v>-1.2747636396757445</v>
+        <v>4.4634638855997819</v>
       </c>
       <c r="G35" s="21">
         <f t="shared" si="38"/>
-        <v>-1.3594775673749302</v>
+        <v>0.25867658107144925</v>
       </c>
       <c r="H35" s="21">
         <f t="shared" si="38"/>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="K35" s="21">
         <f t="shared" si="38"/>
-        <v>-4.4608465699114044</v>
+        <v>1.8882765960234333</v>
       </c>
       <c r="L35" s="21">
         <f t="shared" si="38"/>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="M35" s="21">
         <f t="shared" si="38"/>
-        <v>-8.8091040430794774</v>
+        <v>4.9815839590219522</v>
       </c>
       <c r="N35" s="21">
         <f t="shared" si="38"/>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="W35" s="21">
         <f t="shared" si="39"/>
-        <v>27.376508487800091</v>
+        <v>35.189706476173569</v>
       </c>
       <c r="X35" s="21">
         <f t="shared" si="39"/>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="AI35" s="21">
         <f t="shared" si="39"/>
-        <v>10.273906506988043</v>
+        <v>11.373870374643785</v>
       </c>
       <c r="AJ35" s="21">
         <f t="shared" si="39"/>
@@ -4919,7 +4919,7 @@
         <v>84</v>
       </c>
       <c r="B8" s="27">
-        <v>22967</v>
+        <v>22910</v>
       </c>
       <c r="C8" s="28" t="s">
         <v>99</v>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="B9" s="26">
         <f>IFERROR(AVERAGEIF('Suivi mensuel'!C34:AL34,"&gt;0"),0)</f>
-        <v>22967.375714285707</v>
+        <v>22910.232857142848</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>86</v>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="B10" s="29">
         <f>IF(B8&gt;0,B6/B8,0)</f>
-        <v>0.30478512648582751</v>
+        <v>0.30554343081623747</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>87</v>

--- a/2 FINANCE/TRESORERIE/2026 1028 Modèle Pop Tables - Trésorerie et mois de survie sur 36 mois.xlsx
+++ b/2 FINANCE/TRESORERIE/2026 1028 Modèle Pop Tables - Trésorerie et mois de survie sur 36 mois.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vians\Documents\Claude\Projects\HEC-GEMM-Groupe-7\2 FINANCE\TRESORERIE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A440C5-4377-4CF4-9871-ACC2F192D277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC5F692B-BE94-4253-9917-5DC3A180871D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{2D54D8BB-BD50-4D46-AD8E-735E0D6561AC}"/>
   </bookViews>
@@ -338,9 +338,6 @@
     <t>Suivi mensuel de la trésorerie (36 mois)</t>
   </si>
   <si>
-    <t>SIMULATION mise à jour le 29/10/2026, avant levée de fonds : flux repris du modèle Pop Tables (onglet « Budget 36 mois », référence décidée D-21), selon les décisions D-02 à D-26. Ventes encaissées TTC : places à l'unité en pré-vente le mois qui précède la soirée (D-04), privatisations le mois de la soirée (H). TVA payée aux fournisseurs et reversée à l'État dans « Impôts et TVA ». Investissements (site D-19, matériel) et frais d'ouverture des villes dans « Autres décaissements ». Impôt sur les sociétés non compté. Seul financement compté : la love money de 70 000 € en novembre 2026 (D-26), ligne « Apports ». À remplacer par les montants constatés.</t>
-  </si>
-  <si>
     <t>H : moyenne des mois à consommation positive de la simulation sur 36 mois (ligne 9), à remplacer par la consommation constatée</t>
   </si>
   <si>
@@ -350,7 +347,10 @@
     <t>Pop Tables : soirées gastronomiques éphémères sur le segment du luxe ; places à l'unité en pré-vente et privatisations de salle. Sources : 1 DIRECTION/STRATEGIE/2026 1028 Pop Tables - Cadre de référence (D-02 à D-19) et Business Model Canvas V5 (D-20).</t>
   </si>
   <si>
-    <t>Mis à jour le 29/10/2026 : simulation sur 36 mois reprise du budget Pop Tables (D-21), villes selon D-25, love money de 70 000 € (D-26) ; la société n'est pas créée, aucun relevé n'existe. Tous les montants sont des hypothèses (H).</t>
+    <t>SIMULATION mise à jour le 29/10/2026, avant levée de fonds : flux repris du modèle Pop Tables (onglet « Budget 36 mois », référence décidée D-21), selon les décisions D-02 à D-26. Ventes encaissées TTC : places à l'unité en pré-vente le mois qui précède la soirée (D-04), privatisations le mois de la soirée (H). TVA payée aux fournisseurs et reversée à l'État dans « Impôts et TVA ». Investissements (site D-19, matériel) et frais d'ouverture des villes dans « Autres décaissements ». Impôt sur les sociétés non compté. Seul financement compté : le capital initial de 70 000 €, apporté à parts égales par les 7 fondateurs en novembre 2026 (ligne « Apports »). À remplacer par les montants constatés.</t>
+  </si>
+  <si>
+    <t>Mis à jour le 29/10/2026 : simulation sur 36 mois reprise du budget Pop Tables (D-21), villes selon D-25, capital initial de 70 000 € apporté par les 7 fondateurs ; la société n'est pas créée, aucun relevé n'existe. Tous les montants sont des hypothèses (H).</t>
   </si>
 </sst>
 </file>
@@ -948,7 +948,7 @@
     </row>
     <row r="2" spans="1:2" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="13" x14ac:dyDescent="0.25">
@@ -1044,7 +1044,7 @@
         <v>23</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="13" x14ac:dyDescent="0.25">
@@ -1412,7 +1412,7 @@
     </row>
     <row r="2" spans="1:38" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="31" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:38" ht="13" x14ac:dyDescent="0.3">
@@ -1816,7 +1816,7 @@
         <v>46</v>
       </c>
       <c r="B9" s="18">
-        <f>SUM(C9:AL9)</f>
+        <f t="shared" ref="B9:B15" si="26">SUM(C9:AL9)</f>
         <v>7291000</v>
       </c>
       <c r="C9" s="17">
@@ -1933,7 +1933,7 @@
         <v>47</v>
       </c>
       <c r="B10" s="18">
-        <f>SUM(C10:AL10)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="C10" s="17">
@@ -2050,7 +2050,7 @@
         <v>48</v>
       </c>
       <c r="B11" s="18">
-        <f>SUM(C11:AL11)</f>
+        <f t="shared" si="26"/>
         <v>70000</v>
       </c>
       <c r="C11" s="17">
@@ -2167,7 +2167,7 @@
         <v>49</v>
       </c>
       <c r="B12" s="18">
-        <f>SUM(C12:AL12)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="C12" s="17">
@@ -2284,7 +2284,7 @@
         <v>50</v>
       </c>
       <c r="B13" s="18">
-        <f>SUM(C13:AL13)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="C13" s="17">
@@ -2401,7 +2401,7 @@
         <v>51</v>
       </c>
       <c r="B14" s="18">
-        <f>SUM(C14:AL14)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="C14" s="17">
@@ -2518,151 +2518,151 @@
         <v>52</v>
       </c>
       <c r="B15" s="19">
-        <f>SUM(C15:AL15)</f>
+        <f t="shared" si="26"/>
         <v>7361000</v>
       </c>
       <c r="C15" s="19">
-        <f t="shared" ref="C15:N15" si="26">SUM(C9:C14)</f>
+        <f t="shared" ref="C15:N15" si="27">SUM(C9:C14)</f>
         <v>70000</v>
       </c>
       <c r="D15" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>11600</v>
       </c>
       <c r="E15" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>20700</v>
       </c>
       <c r="F15" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>14700</v>
       </c>
       <c r="G15" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>11600</v>
       </c>
       <c r="H15" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>35700</v>
       </c>
       <c r="I15" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>29700</v>
       </c>
       <c r="J15" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>26600</v>
       </c>
       <c r="K15" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="L15" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>20700</v>
       </c>
       <c r="M15" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>44700</v>
       </c>
       <c r="N15" s="19">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>77000</v>
       </c>
       <c r="O15" s="19">
-        <f t="shared" ref="O15:AL15" si="27">SUM(O9:O14)</f>
+        <f t="shared" ref="O15:AL15" si="28">SUM(O9:O14)</f>
         <v>197000</v>
       </c>
       <c r="P15" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>197000</v>
       </c>
       <c r="Q15" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>197000</v>
       </c>
       <c r="R15" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>197000</v>
       </c>
       <c r="S15" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>197000</v>
       </c>
       <c r="T15" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>197000</v>
       </c>
       <c r="U15" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>197000</v>
       </c>
       <c r="V15" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>197000</v>
       </c>
       <c r="W15" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>150000</v>
       </c>
       <c r="X15" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>197000</v>
       </c>
       <c r="Y15" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>197000</v>
       </c>
       <c r="Z15" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>244000</v>
       </c>
       <c r="AA15" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>394000</v>
       </c>
       <c r="AB15" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>394000</v>
       </c>
       <c r="AC15" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>394000</v>
       </c>
       <c r="AD15" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>394000</v>
       </c>
       <c r="AE15" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>394000</v>
       </c>
       <c r="AF15" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>394000</v>
       </c>
       <c r="AG15" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>394000</v>
       </c>
       <c r="AH15" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>394000</v>
       </c>
       <c r="AI15" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>300000</v>
       </c>
       <c r="AJ15" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>394000</v>
       </c>
       <c r="AK15" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>394000</v>
       </c>
       <c r="AL15" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>394000</v>
       </c>
     </row>
@@ -2713,7 +2713,7 @@
         <v>54</v>
       </c>
       <c r="B17" s="18">
-        <f>SUM(C17:AL17)</f>
+        <f t="shared" ref="B17:B26" si="29">SUM(C17:AL17)</f>
         <v>475000</v>
       </c>
       <c r="C17" s="17">
@@ -2830,7 +2830,7 @@
         <v>55</v>
       </c>
       <c r="B18" s="18">
-        <f>SUM(C18:AL18)</f>
+        <f t="shared" si="29"/>
         <v>892800</v>
       </c>
       <c r="C18" s="17">
@@ -2947,7 +2947,7 @@
         <v>56</v>
       </c>
       <c r="B19" s="18">
-        <f>SUM(C19:AL19)</f>
+        <f t="shared" si="29"/>
         <v>2548451.83</v>
       </c>
       <c r="C19" s="17">
@@ -3064,7 +3064,7 @@
         <v>57</v>
       </c>
       <c r="B20" s="18">
-        <f>SUM(C20:AL20)</f>
+        <f t="shared" si="29"/>
         <v>741295.31999999983</v>
       </c>
       <c r="C20" s="17">
@@ -3181,7 +3181,7 @@
         <v>58</v>
       </c>
       <c r="B21" s="18">
-        <f>SUM(C21:AL21)</f>
+        <f t="shared" si="29"/>
         <v>223557.86999999997</v>
       </c>
       <c r="C21" s="17">
@@ -3298,7 +3298,7 @@
         <v>59</v>
       </c>
       <c r="B22" s="18">
-        <f>SUM(C22:AL22)</f>
+        <f t="shared" si="29"/>
         <v>90200</v>
       </c>
       <c r="C22" s="17">
@@ -3415,7 +3415,7 @@
         <v>60</v>
       </c>
       <c r="B23" s="18">
-        <f>SUM(C23:AL23)</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="C23" s="17">
@@ -3532,7 +3532,7 @@
         <v>61</v>
       </c>
       <c r="B24" s="18">
-        <f>SUM(C24:AL24)</f>
+        <f t="shared" si="29"/>
         <v>761029.46000000008</v>
       </c>
       <c r="C24" s="17">
@@ -3649,7 +3649,7 @@
         <v>62</v>
       </c>
       <c r="B25" s="18">
-        <f>SUM(C25:AL25)</f>
+        <f t="shared" si="29"/>
         <v>752805.21</v>
       </c>
       <c r="C25" s="17">
@@ -3766,151 +3766,151 @@
         <v>63</v>
       </c>
       <c r="B26" s="19">
-        <f>SUM(C26:AL26)</f>
+        <f t="shared" si="29"/>
         <v>6485139.6900000023</v>
       </c>
       <c r="C26" s="19">
-        <f t="shared" ref="C26:N26" si="28">SUM(C17:C25)</f>
+        <f t="shared" ref="C26:N26" si="30">SUM(C17:C25)</f>
         <v>24763</v>
       </c>
       <c r="D26" s="19">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>5351</v>
       </c>
       <c r="E26" s="19">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>12202.629999999997</v>
       </c>
       <c r="F26" s="19">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>25679</v>
       </c>
       <c r="G26" s="19">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>50533.25</v>
       </c>
       <c r="H26" s="19">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>21410.29</v>
       </c>
       <c r="I26" s="19">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>27980.639999999999</v>
       </c>
       <c r="J26" s="19">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>24020.89</v>
       </c>
       <c r="K26" s="19">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>9922.630000000001</v>
       </c>
       <c r="L26" s="19">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>12111</v>
       </c>
       <c r="M26" s="19">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>49268.3</v>
       </c>
       <c r="N26" s="19">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>45308.54</v>
       </c>
       <c r="O26" s="19">
-        <f t="shared" ref="O26:AL26" si="29">SUM(O17:O25)</f>
+        <f t="shared" ref="O26:AL26" si="31">SUM(O17:O25)</f>
         <v>160563.19999999998</v>
       </c>
       <c r="P26" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>154863.19999999998</v>
       </c>
       <c r="Q26" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>155979.39999999997</v>
       </c>
       <c r="R26" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>159930.70999999996</v>
       </c>
       <c r="S26" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>159930.70999999996</v>
       </c>
       <c r="T26" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>159930.70999999996</v>
       </c>
       <c r="U26" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>159930.70999999996</v>
       </c>
       <c r="V26" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>159930.70999999996</v>
       </c>
       <c r="W26" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>159930.70999999996</v>
       </c>
       <c r="X26" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>137754.81</v>
       </c>
       <c r="Y26" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>173979.81999999998</v>
       </c>
       <c r="Z26" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>174930.70999999996</v>
       </c>
       <c r="AA26" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>367064.56</v>
       </c>
       <c r="AB26" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>359874.74</v>
       </c>
       <c r="AC26" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>361274.74</v>
       </c>
       <c r="AD26" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>361274.74</v>
       </c>
       <c r="AE26" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>361274.74</v>
       </c>
       <c r="AF26" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>361274.74</v>
       </c>
       <c r="AG26" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>361274.74</v>
       </c>
       <c r="AH26" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>361274.74</v>
       </c>
       <c r="AI26" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>361274.74</v>
       </c>
       <c r="AJ26" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>282272.95</v>
       </c>
       <c r="AK26" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>359522.95</v>
       </c>
       <c r="AL26" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>361274.74</v>
       </c>
     </row>
@@ -3965,147 +3965,147 @@
         <v>875860.31000000052</v>
       </c>
       <c r="C28" s="19">
-        <f t="shared" ref="C28:N28" si="30">C15-C26</f>
+        <f t="shared" ref="C28:N28" si="32">C15-C26</f>
         <v>45237</v>
       </c>
       <c r="D28" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>6249</v>
       </c>
       <c r="E28" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>8497.3700000000026</v>
       </c>
       <c r="F28" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-10979</v>
       </c>
       <c r="G28" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-38933.25</v>
       </c>
       <c r="H28" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>14289.71</v>
       </c>
       <c r="I28" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>1719.3600000000006</v>
       </c>
       <c r="J28" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>2579.1100000000006</v>
       </c>
       <c r="K28" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-9922.630000000001</v>
       </c>
       <c r="L28" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>8589</v>
       </c>
       <c r="M28" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>-4568.3000000000029</v>
       </c>
       <c r="N28" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>31691.46</v>
       </c>
       <c r="O28" s="19">
-        <f t="shared" ref="O28:AL28" si="31">O15-O26</f>
+        <f t="shared" ref="O28:AL28" si="33">O15-O26</f>
         <v>36436.800000000017</v>
       </c>
       <c r="P28" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>42136.800000000017</v>
       </c>
       <c r="Q28" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>41020.600000000035</v>
       </c>
       <c r="R28" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>37069.290000000037</v>
       </c>
       <c r="S28" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>37069.290000000037</v>
       </c>
       <c r="T28" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>37069.290000000037</v>
       </c>
       <c r="U28" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>37069.290000000037</v>
       </c>
       <c r="V28" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>37069.290000000037</v>
       </c>
       <c r="W28" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-9930.7099999999627</v>
       </c>
       <c r="X28" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>59245.19</v>
       </c>
       <c r="Y28" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>23020.180000000022</v>
       </c>
       <c r="Z28" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>69069.290000000037</v>
       </c>
       <c r="AA28" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>26935.440000000002</v>
       </c>
       <c r="AB28" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>34125.260000000009</v>
       </c>
       <c r="AC28" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>32725.260000000009</v>
       </c>
       <c r="AD28" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>32725.260000000009</v>
       </c>
       <c r="AE28" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>32725.260000000009</v>
       </c>
       <c r="AF28" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>32725.260000000009</v>
       </c>
       <c r="AG28" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>32725.260000000009</v>
       </c>
       <c r="AH28" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>32725.260000000009</v>
       </c>
       <c r="AI28" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-61274.739999999991</v>
       </c>
       <c r="AJ28" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>111727.04999999999</v>
       </c>
       <c r="AK28" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>34477.049999999988</v>
       </c>
       <c r="AL28" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>32725.260000000009</v>
       </c>
     </row>
@@ -4118,147 +4118,147 @@
         <v>875860.31000000052</v>
       </c>
       <c r="C29" s="19">
-        <f t="shared" ref="C29:N29" si="32">C7+C28</f>
+        <f t="shared" ref="C29:N29" si="34">C7+C28</f>
         <v>45237</v>
       </c>
       <c r="D29" s="19">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>51486</v>
       </c>
       <c r="E29" s="19">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>59983.37</v>
       </c>
       <c r="F29" s="19">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>49004.37</v>
       </c>
       <c r="G29" s="19">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>10071.120000000003</v>
       </c>
       <c r="H29" s="19">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>24360.83</v>
       </c>
       <c r="I29" s="19">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>26080.190000000002</v>
       </c>
       <c r="J29" s="19">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>28659.300000000003</v>
       </c>
       <c r="K29" s="19">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>18736.670000000002</v>
       </c>
       <c r="L29" s="19">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>27325.670000000002</v>
       </c>
       <c r="M29" s="19">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>22757.37</v>
       </c>
       <c r="N29" s="19">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>54448.83</v>
       </c>
       <c r="O29" s="19">
-        <f t="shared" ref="O29:AL29" si="33">O7+O28</f>
+        <f t="shared" ref="O29:AL29" si="35">O7+O28</f>
         <v>90885.630000000019</v>
       </c>
       <c r="P29" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>133022.43000000005</v>
       </c>
       <c r="Q29" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>174043.03000000009</v>
       </c>
       <c r="R29" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>211112.32000000012</v>
       </c>
       <c r="S29" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>248181.61000000016</v>
       </c>
       <c r="T29" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>285250.9000000002</v>
       </c>
       <c r="U29" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>322320.19000000024</v>
       </c>
       <c r="V29" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>359389.48000000027</v>
       </c>
       <c r="W29" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>349458.77000000031</v>
       </c>
       <c r="X29" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>408703.96000000031</v>
       </c>
       <c r="Y29" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>431724.14000000036</v>
       </c>
       <c r="Z29" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>500793.4300000004</v>
       </c>
       <c r="AA29" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>527728.87000000034</v>
       </c>
       <c r="AB29" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>561854.13000000035</v>
       </c>
       <c r="AC29" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>594579.39000000036</v>
       </c>
       <c r="AD29" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>627304.65000000037</v>
       </c>
       <c r="AE29" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>660029.91000000038</v>
       </c>
       <c r="AF29" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>692755.17000000039</v>
       </c>
       <c r="AG29" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>725480.4300000004</v>
       </c>
       <c r="AH29" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>758205.69000000041</v>
       </c>
       <c r="AI29" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>696930.95000000042</v>
       </c>
       <c r="AJ29" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>808658.00000000047</v>
       </c>
       <c r="AK29" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>843135.05000000051</v>
       </c>
       <c r="AL29" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>875860.31000000052</v>
       </c>
     </row>
@@ -4309,147 +4309,147 @@
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="19">
-        <f t="shared" ref="C31:N31" si="34">IF(C30="",0,C29-C30)</f>
+        <f t="shared" ref="C31:N31" si="36">IF(C30="",0,C29-C30)</f>
         <v>0</v>
       </c>
       <c r="D31" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="E31" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="F31" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="G31" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="H31" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="I31" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="J31" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="K31" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="L31" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="M31" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="N31" s="19">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="O31" s="19">
-        <f t="shared" ref="O31:AL31" si="35">IF(O30="",0,O29-O30)</f>
+        <f t="shared" ref="O31:AL31" si="37">IF(O30="",0,O29-O30)</f>
         <v>0</v>
       </c>
       <c r="P31" s="19">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="Q31" s="19">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="R31" s="19">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="S31" s="19">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="T31" s="19">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="U31" s="19">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="V31" s="19">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="W31" s="19">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="X31" s="19">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="Y31" s="19">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="Z31" s="19">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AA31" s="19">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AB31" s="19">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AC31" s="19">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AD31" s="19">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AE31" s="19">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AF31" s="19">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AG31" s="19">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AH31" s="19">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AI31" s="19">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AJ31" s="19">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AK31" s="19">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="AL31" s="19">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
     </row>
@@ -4545,147 +4545,147 @@
         <v>-805860.31000000052</v>
       </c>
       <c r="C34" s="19">
-        <f t="shared" ref="C34:N34" si="36">C26-C9-C10-C14</f>
+        <f t="shared" ref="C34:N34" si="38">C26-C9-C10-C14</f>
         <v>24763</v>
       </c>
       <c r="D34" s="19">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-6249</v>
       </c>
       <c r="E34" s="19">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-8497.3700000000026</v>
       </c>
       <c r="F34" s="19">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>10979</v>
       </c>
       <c r="G34" s="19">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>38933.25</v>
       </c>
       <c r="H34" s="19">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-14289.71</v>
       </c>
       <c r="I34" s="19">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-1719.3600000000006</v>
       </c>
       <c r="J34" s="19">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-2579.1100000000006</v>
       </c>
       <c r="K34" s="19">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>9922.630000000001</v>
       </c>
       <c r="L34" s="19">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-8589</v>
       </c>
       <c r="M34" s="19">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>4568.3000000000029</v>
       </c>
       <c r="N34" s="19">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>-31691.46</v>
       </c>
       <c r="O34" s="19">
-        <f t="shared" ref="O34:AL34" si="37">O26-O9-O10-O14</f>
+        <f t="shared" ref="O34:AL34" si="39">O26-O9-O10-O14</f>
         <v>-36436.800000000017</v>
       </c>
       <c r="P34" s="19">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-42136.800000000017</v>
       </c>
       <c r="Q34" s="19">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-41020.600000000035</v>
       </c>
       <c r="R34" s="19">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-37069.290000000037</v>
       </c>
       <c r="S34" s="19">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-37069.290000000037</v>
       </c>
       <c r="T34" s="19">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-37069.290000000037</v>
       </c>
       <c r="U34" s="19">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-37069.290000000037</v>
       </c>
       <c r="V34" s="19">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-37069.290000000037</v>
       </c>
       <c r="W34" s="19">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>9930.7099999999627</v>
       </c>
       <c r="X34" s="19">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-59245.19</v>
       </c>
       <c r="Y34" s="19">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-23020.180000000022</v>
       </c>
       <c r="Z34" s="19">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-69069.290000000037</v>
       </c>
       <c r="AA34" s="19">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-26935.440000000002</v>
       </c>
       <c r="AB34" s="19">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-34125.260000000009</v>
       </c>
       <c r="AC34" s="19">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-32725.260000000009</v>
       </c>
       <c r="AD34" s="19">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-32725.260000000009</v>
       </c>
       <c r="AE34" s="19">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-32725.260000000009</v>
       </c>
       <c r="AF34" s="19">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-32725.260000000009</v>
       </c>
       <c r="AG34" s="19">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-32725.260000000009</v>
       </c>
       <c r="AH34" s="19">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-32725.260000000009</v>
       </c>
       <c r="AI34" s="19">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>61274.739999999991</v>
       </c>
       <c r="AJ34" s="19">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-111727.04999999999</v>
       </c>
       <c r="AK34" s="19">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-34477.049999999988</v>
       </c>
       <c r="AL34" s="19">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>-32725.260000000009</v>
       </c>
     </row>
@@ -4695,147 +4695,147 @@
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="21">
-        <f t="shared" ref="C35:N35" si="38">IF(C34&gt;0,IF(C30&lt;&gt;"",C30,C29)/C34,0)</f>
+        <f t="shared" ref="C35:N35" si="40">IF(C34&gt;0,IF(C30&lt;&gt;"",C30,C29)/C34,0)</f>
         <v>1.8267980454710657</v>
       </c>
       <c r="D35" s="21">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="E35" s="21">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="F35" s="21">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>4.4634638855997819</v>
       </c>
       <c r="G35" s="21">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0.25867658107144925</v>
       </c>
       <c r="H35" s="21">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="I35" s="21">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="J35" s="21">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="K35" s="21">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>1.8882765960234333</v>
       </c>
       <c r="L35" s="21">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="M35" s="21">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>4.9815839590219522</v>
       </c>
       <c r="N35" s="21">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="O35" s="21">
-        <f t="shared" ref="O35:AL35" si="39">IF(O34&gt;0,IF(O30&lt;&gt;"",O30,O29)/O34,0)</f>
+        <f t="shared" ref="O35:AL35" si="41">IF(O34&gt;0,IF(O30&lt;&gt;"",O30,O29)/O34,0)</f>
         <v>0</v>
       </c>
       <c r="P35" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="Q35" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="R35" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="S35" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="T35" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="U35" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="V35" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="W35" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>35.189706476173569</v>
       </c>
       <c r="X35" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="Y35" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="Z35" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AA35" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AB35" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AC35" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AD35" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AE35" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AF35" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AG35" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AH35" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AI35" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>11.373870374643785</v>
       </c>
       <c r="AJ35" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AK35" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AL35" s="21">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
         <v>22910</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="25" x14ac:dyDescent="0.25">
